--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/THBG_0826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/THBG_0826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B980126-050A-4E67-9906-BF54A875482C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69657E57-4B66-4F63-97F6-C2B91ACAA4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -111,15 +111,194 @@
   </si>
   <si>
     <t>TỔNG HỢP PHÍ DỊCH VỤ SỬA CHỮA BẢO HÀNH THÁNG 8/2026</t>
+  </si>
+  <si>
+    <t>TG102LE-4G</t>
+  </si>
+  <si>
+    <t>006080056250512</t>
+  </si>
+  <si>
+    <t>006011074343088</t>
+  </si>
+  <si>
+    <t>Module SIM oxi hoá, 
+lỗi GSM, GPS</t>
+  </si>
+  <si>
+    <t>Module SIM (GPS)</t>
+  </si>
+  <si>
+    <t>Lỗi GPS</t>
+  </si>
+  <si>
+    <t>Chiếc</t>
+  </si>
+  <si>
+    <t>VNSH02</t>
+  </si>
+  <si>
+    <t>0032003F82</t>
+  </si>
+  <si>
+    <t>0032002B3E</t>
+  </si>
+  <si>
+    <t>006011074320466</t>
+  </si>
+  <si>
+    <t>Lỗi khay sim</t>
+  </si>
+  <si>
+    <t>Khay sim nano</t>
+  </si>
+  <si>
+    <t>Module sim (GPS)</t>
+  </si>
+  <si>
+    <t>0032004A24</t>
+  </si>
+  <si>
+    <t>Lỗi khay SIM</t>
+  </si>
+  <si>
+    <t>Khay Nano SIM</t>
+  </si>
+  <si>
+    <t>0032002775</t>
+  </si>
+  <si>
+    <t>00320013AF</t>
+  </si>
+  <si>
+    <t>0032004329</t>
+  </si>
+  <si>
+    <t>VNSH01</t>
+  </si>
+  <si>
+    <t>00BD000993</t>
+  </si>
+  <si>
+    <t>Module GPS</t>
+  </si>
+  <si>
+    <t>00BD000CC2</t>
+  </si>
+  <si>
+    <t>Lỗi nguồn</t>
+  </si>
+  <si>
+    <t>IC điều khiển nguồn</t>
+  </si>
+  <si>
+    <t>006011074328386</t>
+  </si>
+  <si>
+    <t>0032001125</t>
+  </si>
+  <si>
+    <t>Lỗi Module GPS</t>
+  </si>
+  <si>
+    <t>Thay Module GPS</t>
+  </si>
+  <si>
+    <t>006011074343138</t>
+  </si>
+  <si>
+    <t>003200137D</t>
+  </si>
+  <si>
+    <t>Không quay được số</t>
+  </si>
+  <si>
+    <t>Thay Module SIM</t>
+  </si>
+  <si>
+    <t>Phí sửa chữa đã thanh toán cho kế toán (25/08/2026)</t>
+  </si>
+  <si>
+    <t>007785070558377</t>
+  </si>
+  <si>
+    <t>007785070554368</t>
+  </si>
+  <si>
+    <t>Không có dịch vụ mạng</t>
+  </si>
+  <si>
+    <t>Kích hoạt lại dịch vụ eSIM</t>
+  </si>
+  <si>
+    <t>003200706B</t>
+  </si>
+  <si>
+    <t>0032004CDA</t>
+  </si>
+  <si>
+    <t>Thường xuyên mất GPS</t>
+  </si>
+  <si>
+    <t>Thay module GPS</t>
+  </si>
+  <si>
+    <t>Công nợ ghi 
+CSKH Hương</t>
+  </si>
+  <si>
+    <t>003200126C</t>
+  </si>
+  <si>
+    <t>Đại lý Anh 
+Hồng Phú Thọ</t>
+  </si>
+  <si>
+    <t>Đại lý Anh Trực</t>
+  </si>
+  <si>
+    <t>Đại lý Anh 
+Tuấn Bắc Giang</t>
+  </si>
+  <si>
+    <t>Đại lý Anh 
+Tuấn Ninh Bình</t>
+  </si>
+  <si>
+    <t>Đại lý Gia Thành</t>
+  </si>
+  <si>
+    <t>Đại lý Hoàng Anh Nghệ An</t>
+  </si>
+  <si>
+    <t>Đại lý Ngọc Hoàn</t>
+  </si>
+  <si>
+    <t>Đại lý SEA</t>
+  </si>
+  <si>
+    <t>Đại lý Thành 
+Tâm Nha Trang</t>
+  </si>
+  <si>
+    <t>Đại lý Victory</t>
+  </si>
+  <si>
+    <t>Công nợ ghi 
+kinh doanh</t>
+  </si>
+  <si>
+    <t>Công nợ 
+ghi kinh doanh</t>
+  </si>
+  <si>
+    <t>Đại lý Nguyễn Cương</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="@*."/>
-  </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -221,7 +400,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,8 +413,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -375,11 +560,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -470,17 +692,14 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -522,26 +741,56 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,15 +814,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>225838</xdr:colOff>
+      <xdr:colOff>328414</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>168518</xdr:rowOff>
+      <xdr:rowOff>161192</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>402980</xdr:colOff>
+      <xdr:colOff>388325</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>58615</xdr:rowOff>
+      <xdr:rowOff>51289</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -602,7 +851,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="584857" y="168518"/>
+          <a:off x="687433" y="161192"/>
           <a:ext cx="2089469" cy="527539"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -905,11 +1154,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="1" customWidth="1"/>
@@ -928,87 +1177,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38" t="s">
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="40"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="39"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="41" t="s">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="44" t="s">
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="46"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="47" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="49"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="48"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1020,12 +1269,12 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="8"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -1070,417 +1319,893 @@
       </c>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="21"/>
+    <row r="9" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>1</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="19">
+        <v>1</v>
+      </c>
+      <c r="J9" s="21">
+        <v>200000</v>
+      </c>
+      <c r="K9" s="21">
+        <f>SUM(I9*J9)</f>
+        <v>200000</v>
+      </c>
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="21"/>
+      <c r="A10" s="19">
+        <v>2</v>
+      </c>
+      <c r="B10" s="62"/>
+      <c r="C10" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="58"/>
+      <c r="F10" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="19">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21">
+        <v>200000</v>
+      </c>
+      <c r="K10" s="21">
+        <f>SUM(I10*J10)</f>
+        <v>200000</v>
+      </c>
       <c r="AB10" s="2"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="21"/>
+      <c r="A11" s="19">
+        <v>3</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="19">
+        <v>1</v>
+      </c>
+      <c r="J11" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K11" s="21">
+        <f t="shared" ref="K11:K28" si="0">SUM(I11*J11)</f>
+        <v>130000</v>
+      </c>
       <c r="AB11" s="2"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="21"/>
+      <c r="A12" s="19">
+        <v>4</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="F12" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="19">
+        <v>1</v>
+      </c>
+      <c r="J12" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K12" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="33"/>
+      <c r="A13" s="19">
+        <v>5</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="58"/>
+      <c r="F13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="19">
+        <v>1</v>
+      </c>
+      <c r="J13" s="21">
+        <v>200000</v>
+      </c>
+      <c r="K13" s="21">
+        <f t="shared" si="0"/>
+        <v>200000</v>
+      </c>
+      <c r="L13" s="32"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+    <row r="14" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>6</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="58"/>
+      <c r="F14" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="19">
+        <v>1</v>
+      </c>
+      <c r="J14" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K14" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
+    <row r="15" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>7</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="19">
+        <v>1</v>
+      </c>
+      <c r="J15" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K15" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
+      <c r="A16" s="19">
+        <v>8</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="58"/>
+      <c r="F16" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="19">
+        <v>1</v>
+      </c>
+      <c r="J16" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K16" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
       <c r="AB16" s="2"/>
     </row>
     <row r="17" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
+      <c r="A17" s="19">
+        <v>9</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="58"/>
+      <c r="F17" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="19">
+        <v>1</v>
+      </c>
+      <c r="J17" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K17" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
       <c r="AB17" s="2"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
+      <c r="A18" s="19">
+        <v>10</v>
+      </c>
+      <c r="B18" s="62"/>
+      <c r="C18" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="58"/>
+      <c r="F18" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="19">
+        <v>1</v>
+      </c>
+      <c r="J18" s="21">
+        <v>230000</v>
+      </c>
+      <c r="K18" s="21">
+        <f t="shared" si="0"/>
+        <v>230000</v>
+      </c>
       <c r="AB18" s="2"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
+      <c r="A19" s="19">
+        <v>11</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="58"/>
+      <c r="F19" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="19">
+        <v>1</v>
+      </c>
+      <c r="J19" s="21">
+        <v>150000</v>
+      </c>
+      <c r="K19" s="21">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
+    <row r="20" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>12</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="58"/>
+      <c r="F20" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="19">
+        <v>1</v>
+      </c>
+      <c r="J20" s="21">
+        <v>200000</v>
+      </c>
+      <c r="K20" s="21">
+        <f t="shared" si="0"/>
+        <v>200000</v>
+      </c>
       <c r="AB20" s="2"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
+      <c r="A21" s="19">
+        <v>13</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="58"/>
+      <c r="F21" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="19">
+        <v>1</v>
+      </c>
+      <c r="J21" s="21">
+        <v>260000</v>
+      </c>
+      <c r="K21" s="21">
+        <f t="shared" si="0"/>
+        <v>260000</v>
+      </c>
       <c r="AB21" s="2"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
+    <row r="22" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>14</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="59"/>
+      <c r="F22" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="19">
+        <v>1</v>
+      </c>
+      <c r="J22" s="21">
+        <v>200000</v>
+      </c>
+      <c r="K22" s="21">
+        <f t="shared" si="0"/>
+        <v>200000</v>
+      </c>
       <c r="AB22" s="2"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="10"/>
+    <row r="23" spans="1:28" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>15</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="19">
+        <v>1</v>
+      </c>
+      <c r="J23" s="21">
+        <v>600000</v>
+      </c>
+      <c r="K23" s="21">
+        <f t="shared" si="0"/>
+        <v>600000</v>
+      </c>
       <c r="AB23" s="2"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="26"/>
+      <c r="A24" s="19">
+        <v>16</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="19">
+        <v>1</v>
+      </c>
+      <c r="J24" s="21">
+        <v>50000</v>
+      </c>
+      <c r="K24" s="21">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
       <c r="AB24" s="2"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="19">
+        <v>17</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="61"/>
+      <c r="F25" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="19">
+        <v>1</v>
+      </c>
+      <c r="J25" s="21">
+        <v>50000</v>
+      </c>
+      <c r="K25" s="21">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
+      <c r="AB25" s="2"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>18</v>
+      </c>
+      <c r="B26" s="61"/>
+      <c r="C26" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="61"/>
+      <c r="F26" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="19">
+        <v>1</v>
+      </c>
+      <c r="J26" s="21">
+        <v>260000</v>
+      </c>
+      <c r="K26" s="21">
+        <f t="shared" si="0"/>
+        <v>260000</v>
+      </c>
+      <c r="AB26" s="2"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>19</v>
+      </c>
+      <c r="B27" s="62"/>
+      <c r="C27" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="62"/>
+      <c r="F27" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="19">
+        <v>1</v>
+      </c>
+      <c r="J27" s="21">
+        <v>260000</v>
+      </c>
+      <c r="K27" s="21">
+        <f t="shared" si="0"/>
+        <v>260000</v>
+      </c>
+      <c r="AB27" s="2"/>
+    </row>
+    <row r="28" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>20</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="19">
+        <v>1</v>
+      </c>
+      <c r="J28" s="21">
+        <v>130000</v>
+      </c>
+      <c r="K28" s="21">
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="AB28" s="2"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="10"/>
+      <c r="AB29" s="2"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="26"/>
+      <c r="AB30" s="2"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35" t="s">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35" t="s">
+      <c r="E31" s="50"/>
+      <c r="F31" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35" t="s">
+      <c r="G31" s="50"/>
+      <c r="H31" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="AB25" s="2"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="AB31" s="2"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34" t="s">
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34" t="s">
+      <c r="E32" s="49"/>
+      <c r="F32" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34" t="s">
+      <c r="G32" s="49"/>
+      <c r="H32" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="AB26" s="2"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="29"/>
-      <c r="AB27" s="2"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="AB32" s="2"/>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="29"/>
+      <c r="AB33" s="2"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="30"/>
-      <c r="AB28" s="2"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="30"/>
-      <c r="AB29" s="2"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="30"/>
-      <c r="AB30" s="2"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+      <c r="H34" s="14"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="30"/>
+      <c r="AB34" s="2"/>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="30"/>
+      <c r="AB35" s="2"/>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="30"/>
+      <c r="AB36" s="2"/>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36" t="s">
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36" t="s">
+      <c r="E37" s="51"/>
+      <c r="F37" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36" t="s">
+      <c r="G37" s="51"/>
+      <c r="H37" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="11"/>
-      <c r="AB31" s="2"/>
-    </row>
-    <row r="32" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="31"/>
-      <c r="AB32" s="2"/>
-    </row>
-    <row r="33" spans="7:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="G33" s="4"/>
-      <c r="AB33" s="2"/>
-    </row>
-    <row r="34" spans="7:28" x14ac:dyDescent="0.25">
-      <c r="AB34" s="2"/>
-    </row>
-    <row r="35" spans="7:28" x14ac:dyDescent="0.25">
-      <c r="AB35" s="2"/>
-    </row>
-    <row r="36" spans="7:28" x14ac:dyDescent="0.25">
-      <c r="AB36" s="2"/>
-    </row>
-    <row r="37" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="11"/>
       <c r="AB37" s="2"/>
     </row>
-    <row r="38" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="31"/>
       <c r="AB38" s="2"/>
     </row>
-    <row r="39" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="G39" s="4"/>
       <c r="AB39" s="2"/>
     </row>
-    <row r="40" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB40" s="2"/>
     </row>
-    <row r="41" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB41" s="2"/>
     </row>
-    <row r="42" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB42" s="2"/>
     </row>
-    <row r="43" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB43" s="2"/>
     </row>
-    <row r="44" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB44" s="2"/>
     </row>
-    <row r="45" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB45" s="2"/>
     </row>
-    <row r="46" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB46" s="2"/>
     </row>
-    <row r="47" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB47" s="2"/>
     </row>
-    <row r="48" spans="7:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB48" s="2"/>
     </row>
     <row r="49" spans="28:28" x14ac:dyDescent="0.25">
@@ -1492,9 +2217,45 @@
     <row r="51" spans="28:28" x14ac:dyDescent="0.25">
       <c r="AB51" s="2"/>
     </row>
+    <row r="52" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB52" s="2"/>
+    </row>
+    <row r="53" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB53" s="2"/>
+    </row>
+    <row r="54" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB54" s="2"/>
+    </row>
+    <row r="55" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB55" s="2"/>
+    </row>
+    <row r="56" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB56" s="2"/>
+    </row>
+    <row r="57" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB57" s="2"/>
+    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="20">
+  <mergeCells count="26">
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="E9:E22"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
@@ -1503,24 +2264,12 @@
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="86" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="73" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/THBG_0826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/THBG_0826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69657E57-4B66-4F63-97F6-C2B91ACAA4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A66DD0B-6F89-41E8-9373-EE2A46F0CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -693,6 +693,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -701,6 +743,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -739,57 +787,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,87 +1174,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="39"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="55"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="40" t="s">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="42"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="58"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="43" t="s">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="45"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="61"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="46" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="64"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1269,12 +1266,12 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -1323,19 +1320,19 @@
       <c r="A9" s="19">
         <v>1</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="39" t="s">
         <v>74</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="34" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="20" t="s">
@@ -1360,15 +1357,15 @@
       <c r="A10" s="19">
         <v>2</v>
       </c>
-      <c r="B10" s="62"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="53" t="s">
+      <c r="E10" s="42"/>
+      <c r="F10" s="34" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="20" t="s">
@@ -1393,7 +1390,7 @@
       <c r="A11" s="19">
         <v>3</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="39" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -1402,8 +1399,8 @@
       <c r="D11" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="56" t="s">
+      <c r="E11" s="42"/>
+      <c r="F11" s="37" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -1428,15 +1425,15 @@
       <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="20" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="56" t="s">
+      <c r="E12" s="42"/>
+      <c r="F12" s="37" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="20" t="s">
@@ -1461,14 +1458,14 @@
       <c r="A13" s="19">
         <v>5</v>
       </c>
-      <c r="B13" s="62"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="58"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="20" t="s">
         <v>34</v>
       </c>
@@ -1501,11 +1498,11 @@
       <c r="C14" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="58"/>
-      <c r="F14" s="53" t="s">
+      <c r="E14" s="42"/>
+      <c r="F14" s="34" t="s">
         <v>44</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -1530,17 +1527,17 @@
       <c r="A15" s="19">
         <v>7</v>
       </c>
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="39" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="54" t="s">
+      <c r="E15" s="42"/>
+      <c r="F15" s="35" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="20" t="s">
@@ -1565,15 +1562,15 @@
       <c r="A16" s="19">
         <v>8</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="54" t="s">
+      <c r="E16" s="42"/>
+      <c r="F16" s="35" t="s">
         <v>44</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -1598,15 +1595,15 @@
       <c r="A17" s="19">
         <v>9</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="54" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="53" t="s">
+      <c r="E17" s="42"/>
+      <c r="F17" s="34" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="20" t="s">
@@ -1631,15 +1628,15 @@
       <c r="A18" s="19">
         <v>10</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="54" t="s">
+      <c r="B18" s="41"/>
+      <c r="C18" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="53" t="s">
+      <c r="E18" s="42"/>
+      <c r="F18" s="34" t="s">
         <v>34</v>
       </c>
       <c r="G18" s="20" t="s">
@@ -1667,14 +1664,14 @@
       <c r="B19" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="53" t="s">
+      <c r="E19" s="42"/>
+      <c r="F19" s="34" t="s">
         <v>53</v>
       </c>
       <c r="G19" s="20" t="s">
@@ -1702,14 +1699,14 @@
       <c r="B20" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="53" t="s">
+      <c r="E20" s="42"/>
+      <c r="F20" s="34" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="20" t="s">
@@ -1737,14 +1734,14 @@
       <c r="B21" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="53" t="s">
+      <c r="E21" s="42"/>
+      <c r="F21" s="34" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -1772,14 +1769,14 @@
       <c r="B22" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="53" t="s">
+      <c r="E22" s="43"/>
+      <c r="F22" s="34" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="20" t="s">
@@ -1807,16 +1804,16 @@
       <c r="B23" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="35" t="s">
         <v>60</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="34" t="s">
         <v>61</v>
       </c>
       <c r="G23" s="20" t="s">
@@ -1841,19 +1838,19 @@
       <c r="A24" s="19">
         <v>16</v>
       </c>
-      <c r="B24" s="60" t="s">
+      <c r="B24" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="60" t="s">
+      <c r="E24" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="54" t="s">
+      <c r="F24" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="20" t="s">
@@ -1878,15 +1875,15 @@
       <c r="A25" s="19">
         <v>17</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="54" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="54" t="s">
+      <c r="E25" s="40"/>
+      <c r="F25" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -1911,15 +1908,15 @@
       <c r="A26" s="19">
         <v>18</v>
       </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="54" t="s">
+      <c r="B26" s="40"/>
+      <c r="C26" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="54" t="s">
+      <c r="E26" s="40"/>
+      <c r="F26" s="35" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -1944,15 +1941,15 @@
       <c r="A27" s="19">
         <v>19</v>
       </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="54" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="54" t="s">
+      <c r="E27" s="41"/>
+      <c r="F27" s="35" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -2039,47 +2036,47 @@
       <c r="AB30" s="2"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50" t="s">
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50" t="s">
+      <c r="E31" s="44"/>
+      <c r="F31" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50" t="s">
+      <c r="G31" s="44"/>
+      <c r="H31" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
       <c r="AB31" s="2"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49" t="s">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49" t="s">
+      <c r="E32" s="45"/>
+      <c r="F32" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49" t="s">
+      <c r="G32" s="45"/>
+      <c r="H32" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
       <c r="AB32" s="2"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
@@ -2141,25 +2138,25 @@
       <c r="AB36" s="2"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51" t="s">
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51" t="s">
+      <c r="E37" s="46"/>
+      <c r="F37" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51" t="s">
+      <c r="G37" s="46"/>
+      <c r="H37" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="11"/>
       <c r="AB37" s="2"/>
     </row>
@@ -2238,24 +2235,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="E9:E22"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="F37:G37"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
@@ -2264,12 +2243,30 @@
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="E9:E22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="73" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="1" right="1" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>